--- a/docs/build/lakeshore-enterprise-context/source/06_it_systems_architecture/legacy_applications.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/06_it_systems_architecture/legacy_applications.xlsx
@@ -437,7 +437,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -485,15 +485,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Access DB 0</t>
+          <t>Mainframe GL 0</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -510,15 +510,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mainframe GL 1</t>
+          <t>VB6 Pricing 1</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -535,15 +535,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mainframe GL 2</t>
+          <t>Access DB 2</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -560,15 +560,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Access DB 3</t>
+          <t>AS/400 Billing 3</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -585,11 +585,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VB6 Pricing 4</t>
+          <t>Mainframe GL 4</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -610,11 +610,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Access DB 5</t>
+          <t>Mainframe GL 5</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -635,15 +635,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VB6 Pricing 6</t>
+          <t>Access DB 6</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -664,11 +664,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -685,11 +685,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lotus Notes 8</t>
+          <t>Access DB 8</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -710,11 +710,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Access DB 9</t>
+          <t>VB6 Pricing 9</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -735,15 +735,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mainframe GL 10</t>
+          <t>VB6 Pricing 10</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -760,11 +760,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mainframe GL 11</t>
+          <t>Lotus Notes 11</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -785,15 +785,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lotus Notes 12</t>
+          <t>Access DB 12</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -810,11 +810,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Access DB 13</t>
+          <t>Mainframe GL 13</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -835,15 +835,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lotus Notes 14</t>
+          <t>Mainframe GL 14</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -864,11 +864,11 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -935,15 +935,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Access DB 18</t>
+          <t>Lotus Notes 18</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -960,15 +960,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lotus Notes 19</t>
+          <t>Access DB 19</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
